--- a/CodeSystem-ng-lgas-cs.xlsx
+++ b/CodeSystem-ng-lgas-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:22:49+01:00</t>
+    <t>2026-08-17T07:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ng-lgas-cs.xlsx
+++ b/CodeSystem-ng-lgas-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T07:55:48+01:00</t>
+    <t>2026-08-17T13:27:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ng-lgas-cs.xlsx
+++ b/CodeSystem-ng-lgas-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T13:27:53+01:00</t>
+    <t>2026-08-17T16:10:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ng-lgas-cs.xlsx
+++ b/CodeSystem-ng-lgas-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T06:18:50+01:00</t>
+    <t>2026-08-18T15:57:17+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ng-lgas-cs.xlsx
+++ b/CodeSystem-ng-lgas-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:57:17+01:00</t>
+    <t>2026-08-18T16:47:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
